--- a/louvain_baseline_experiments/louvain_Baseline_summary.xlsx
+++ b/louvain_baseline_experiments/louvain_Baseline_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,12 +506,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>louvain_Baseline_lesmis</t>
+          <t>louvain_Baseline_soc-dolphins_normalized</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lesmis</t>
+          <t>soc-dolphins_normalized</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F2" t="n">
-        <v>254</v>
+        <v>159</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08680792891319207</v>
+        <v>0.08408249603384453</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -543,139 +543,19 @@
         <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5658216835217148</v>
+        <v>0.5165539337842615</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5658216835217132</v>
+        <v>0.516553933784265</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001975599996512756</v>
+        <v>0.001790599999367259</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02588190000096802</v>
+        <v>0.02540969999972731</v>
       </c>
       <c r="P2" t="n">
-        <v>0.07626960000197869</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>louvain_Baseline</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>louvain_Baseline_football</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>louvain</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>115</v>
-      </c>
-      <c r="F3" t="n">
-        <v>612</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.09336384439359267</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.5961082473540856</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.5961082473540925</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.001884500001324341</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.009956299996702</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.02061669999966398</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>louvain_Baseline</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>louvain_Baseline_celegans_edges</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>celegans_edges</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>louvain</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>297</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1918</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.04363454363454364</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>26</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.4190027138190354</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.4190027138190374</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.01323650000267662</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.07029459999466781</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.1168926999962423</v>
+        <v>0.1204557000019122</v>
       </c>
     </row>
   </sheetData>

--- a/louvain_baseline_experiments/louvain_Baseline_summary.xlsx
+++ b/louvain_baseline_experiments/louvain_Baseline_summary.xlsx
@@ -506,12 +506,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>louvain_Baseline_soc-dolphins_normalized</t>
+          <t>louvain_Baseline_arenas-jazz_normalized</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>soc-dolphins_normalized</t>
+          <t>arenas-jazz_normalized</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>62</v>
+        <v>198</v>
       </c>
       <c r="F2" t="n">
-        <v>159</v>
+        <v>2742</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08408249603384453</v>
+        <v>0.1405937548069528</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -540,22 +540,22 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5165539337842615</v>
+        <v>0.445026802990566</v>
       </c>
       <c r="M2" t="n">
-        <v>0.516553933784265</v>
+        <v>0.4450268029905711</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001790599999367259</v>
+        <v>0.01028739999992467</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02540969999972731</v>
+        <v>0.05012560000022859</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1204557000019122</v>
+        <v>0.1805820999998105</v>
       </c>
     </row>
   </sheetData>

--- a/louvain_baseline_experiments/louvain_Baseline_summary.xlsx
+++ b/louvain_baseline_experiments/louvain_Baseline_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,12 +506,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>louvain_Baseline_arenas-jazz_normalized</t>
+          <t>louvain_Baseline_brock200-3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>arenas-jazz_normalized</t>
+          <t>brock200-3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F2" t="n">
-        <v>2742</v>
+        <v>12048</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1405937548069528</v>
+        <v>0.605427135678392</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -540,22 +540,862 @@
         </is>
       </c>
       <c r="K2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.04073588131427447</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.04073588131427366</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.03294589999859454</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1509097000016482</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.2523004000031506</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>louvain_Baseline</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>louvain_Baseline_CAG_mat72</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CAG_mat72</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>louvain</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>72</v>
+      </c>
+      <c r="F3" t="n">
+        <v>678</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2652582159624413</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.4824797231451564</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.4824797231451569</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001061599999957252</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.007946099998662248</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.01724980000290088</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>louvain_Baseline</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>louvain_Baseline_ca-sandi_auths</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ca-sandi_auths</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>louvain</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>86</v>
+      </c>
+      <c r="F4" t="n">
+        <v>124</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.03392612859097127</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.7311265432098727</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.7311265432098766</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0008454000053461641</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.005182900000363588</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.01302310000028228</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>louvain_Baseline</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>louvain_Baseline_chesapeake</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>chesapeake</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>louvain</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>39</v>
+      </c>
+      <c r="F5" t="n">
+        <v>170</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2294197031039136</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.2366089965397935</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2366089965397924</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0003848999986075796</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.003385600000910927</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.009499200001300778</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>louvain_Baseline</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>louvain_Baseline_eco-florida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>eco-florida</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>louvain</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>128</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2075</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2552903543307087</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>4</v>
       </c>
-      <c r="L2" t="n">
-        <v>0.445026802990566</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.4450268029905711</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.01028739999992467</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.05012560000022859</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.1805820999998105</v>
+      <c r="L6" t="n">
+        <v>0.3630110985695624</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.3630110985695627</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.003304999998363201</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0202865000028396</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.03812859999743523</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>louvain_Baseline</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>louvain_Baseline_eco-mangwet</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>eco-mangwet</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>louvain</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>97</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1446</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3105670103092784</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2216361559298658</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2216361559298668</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.002136800001608208</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.01580390000162879</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.03062599999975646</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>louvain_Baseline</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>louvain_Baseline_econ-wm3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>econ-wm3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>louvain</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>260</v>
+      </c>
+      <c r="F8" t="n">
+        <v>733</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.02177012177012177</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>33</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.57722783907811</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.7433358450682034</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.006088900001486763</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0255745999966166</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.05484060000162572</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>louvain_Baseline</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>louvain_Baseline_ENZYMES123</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ENZYMES123</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>louvain</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>90</v>
+      </c>
+      <c r="F9" t="n">
+        <v>127</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0317103620474407</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.68578337156675</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.6857833715667431</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.000865699999849312</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.006099199999880511</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.01450789999944391</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>louvain_Baseline</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>louvain_Baseline_inf-USAir97</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>inf-USAir97</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>louvain</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>332</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2126</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0386925344884068</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.1971651377669547</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1971651377669546</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.01103680000232998</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.04249320000235457</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.09138620000157971</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>louvain_Baseline</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>louvain_Baseline_insecta-ant-colony2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>insecta-ant-colony2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>louvain</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>131</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8437</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9908396946564886</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.2447110721340678</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2447110721340677</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.008374900004127994</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05531999999948312</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.08364119999896502</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>louvain_Baseline</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>louvain_Baseline_johnson8-4-4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>johnson8-4-4</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>louvain</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>70</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1855</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7681159420289855</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.03557951482479821</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.03557951482479781</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.002143099998647813</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.01737909999792464</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.02706649999890942</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>louvain_Baseline</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>louvain_Baseline_reptilia-tortoise-network-bsv</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>reptilia-tortoise-network-bsv</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>louvain</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>136</v>
+      </c>
+      <c r="F13" t="n">
+        <v>374</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.04074074074074074</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.628746877016397</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.6287468770163975</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.001996500002860557</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0111278999975184</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.02382599999691593</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>louvain_Baseline</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>louvain_Baseline_road-chesapeake</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>road-chesapeake</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>louvain</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>39</v>
+      </c>
+      <c r="F14" t="n">
+        <v>170</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.2294197031039136</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2366089965397935</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2366089965397924</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.0003378999972483143</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.003283500001998618</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.009585100000549573</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>louvain_Baseline</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>louvain_Baseline_sociopatterns-hypertext</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>sociopatterns-hypertext</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>louvain</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>113</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2196</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.3470290771175727</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>9</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5152676720147695</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.5152676720147689</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.003197100006218534</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.02482579999923473</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.03766239999822574</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>louvain_Baseline</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>louvain_Baseline_SW-100-6-0d1-trial2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SW-100-6-0d1-trial2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>louvain</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
+      <c r="F16" t="n">
+        <v>300</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.6448833333333298</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.6448833333333333</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.001176999998278916</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.008294500003103167</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.01750030000403058</v>
       </c>
     </row>
   </sheetData>

--- a/louvain_baseline_experiments/louvain_Baseline_summary.xlsx
+++ b/louvain_baseline_experiments/louvain_Baseline_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,12 +506,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>louvain_Baseline_brock200-3</t>
+          <t>louvain_Baseline_synthetic_50_clear_four_blocks</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>brock200-3</t>
+          <t>synthetic_50_clear_four_blocks</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>12048</v>
+        <v>169</v>
       </c>
       <c r="G2" t="n">
-        <v>0.605427135678392</v>
+        <v>0.1379591836734694</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -540,22 +540,22 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04073588131427447</v>
+        <v>0.7019216158959747</v>
       </c>
       <c r="M2" t="n">
-        <v>0.04073588131427366</v>
+        <v>0.701921615895975</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03294589999859454</v>
+        <v>0.001589499996043742</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1509097000016482</v>
+        <v>0.005063099990366027</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2523004000031506</v>
+        <v>0.0537975000042934</v>
       </c>
     </row>
     <row r="3">
@@ -566,12 +566,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>louvain_Baseline_CAG_mat72</t>
+          <t>louvain_Baseline_synthetic_50_core_periphery_bridge</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CAG_mat72</t>
+          <t>synthetic_50_core_periphery_bridge</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>678</v>
+        <v>209</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2652582159624413</v>
+        <v>0.1706122448979592</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4824797231451564</v>
+        <v>0.4201059097601256</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4824797231451569</v>
+        <v>0.4201059097601264</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001061599999957252</v>
+        <v>0.0004570000019157305</v>
       </c>
       <c r="O3" t="n">
-        <v>0.007946099998662248</v>
+        <v>0.00473289999354165</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01724980000290088</v>
+        <v>0.01121229999989737</v>
       </c>
     </row>
     <row r="4">
@@ -626,12 +626,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>louvain_Baseline_ca-sandi_auths</t>
+          <t>louvain_Baseline_synthetic_100_fuzzy_mixed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ca-sandi_auths</t>
+          <t>synthetic_100_fuzzy_mixed</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>124</v>
+        <v>540</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03392612859097127</v>
+        <v>0.1090909090909091</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7311265432098727</v>
+        <v>0.4947962521562994</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7311265432098766</v>
+        <v>0.4947962521562985</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0008454000053461641</v>
+        <v>0.001586099999258295</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005182900000363588</v>
+        <v>0.01223120000213385</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01302310000028228</v>
+        <v>0.02225969999562949</v>
       </c>
     </row>
     <row r="5">
@@ -686,12 +686,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>louvain_Baseline_chesapeake</t>
+          <t>louvain_Baseline_synthetic_100_hierarchical</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>chesapeake</t>
+          <t>synthetic_100_hierarchical</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>170</v>
+        <v>376</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2294197031039136</v>
+        <v>0.07595959595959596</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -720,22 +720,22 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2366089965397935</v>
+        <v>0.7641841184440451</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2366089965397924</v>
+        <v>0.7641841184440454</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0003848999986075796</v>
+        <v>0.001293300010729581</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003385600000910927</v>
+        <v>0.009049299987964332</v>
       </c>
       <c r="P5" t="n">
-        <v>0.009499200001300778</v>
+        <v>0.01843210001243278</v>
       </c>
     </row>
     <row r="6">
@@ -746,12 +746,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>louvain_Baseline_eco-florida</t>
+          <t>louvain_Baseline_synthetic_150_hub_modular</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>eco-florida</t>
+          <t>synthetic_150_hub_modular</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="F6" t="n">
-        <v>2075</v>
+        <v>622</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2552903543307087</v>
+        <v>0.05565995525727069</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -780,22 +780,22 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3630110985695624</v>
+        <v>0.7629163455252623</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3630110985695627</v>
+        <v>0.7629163455252603</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003304999998363201</v>
+        <v>0.002554000006057322</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0202865000028396</v>
+        <v>0.009040500008268282</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03812859999743523</v>
+        <v>0.02336549999017734</v>
       </c>
     </row>
     <row r="7">
@@ -806,12 +806,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>louvain_Baseline_eco-mangwet</t>
+          <t>louvain_Baseline_synthetic_150_ring_bottleneck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>eco-mangwet</t>
+          <t>synthetic_150_ring_bottleneck</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -820,13 +820,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>97</v>
+        <v>150</v>
       </c>
       <c r="F7" t="n">
-        <v>1446</v>
+        <v>575</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3105670103092784</v>
+        <v>0.05145413870246085</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -840,562 +840,22 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2216361559298658</v>
+        <v>0.8171050281359142</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2216361559298668</v>
+        <v>0.8171050281359094</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002136800001608208</v>
+        <v>0.002651000002515502</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01580390000162879</v>
+        <v>0.01528039999539033</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03062599999975646</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>louvain_Baseline</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>louvain_Baseline_econ-wm3</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>econ-wm3</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>louvain</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>260</v>
-      </c>
-      <c r="F8" t="n">
-        <v>733</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.02177012177012177</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>33</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2.57722783907811</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.7433358450682034</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.006088900001486763</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.0255745999966166</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.05484060000162572</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>louvain_Baseline</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>louvain_Baseline_ENZYMES123</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ENZYMES123</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>louvain</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>90</v>
-      </c>
-      <c r="F9" t="n">
-        <v>127</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.0317103620474407</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>9</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.68578337156675</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.6857833715667431</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.000865699999849312</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.006099199999880511</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.01450789999944391</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>louvain_Baseline</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>louvain_Baseline_inf-USAir97</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>inf-USAir97</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>louvain</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>332</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2126</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.0386925344884068</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.1971651377669547</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.1971651377669546</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.01103680000232998</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.04249320000235457</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.09138620000157971</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>louvain_Baseline</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>louvain_Baseline_insecta-ant-colony2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>insecta-ant-colony2</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>louvain</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>131</v>
-      </c>
-      <c r="F11" t="n">
-        <v>8437</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.9908396946564886</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.2447110721340678</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.2447110721340677</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.008374900004127994</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.05531999999948312</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.08364119999896502</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>louvain_Baseline</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>louvain_Baseline_johnson8-4-4</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>johnson8-4-4</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>louvain</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>70</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1855</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.7681159420289855</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.03557951482479821</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.03557951482479781</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.002143099998647813</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.01737909999792464</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.02706649999890942</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>louvain_Baseline</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>louvain_Baseline_reptilia-tortoise-network-bsv</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>reptilia-tortoise-network-bsv</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>louvain</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>136</v>
-      </c>
-      <c r="F13" t="n">
-        <v>374</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.04074074074074074</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.628746877016397</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.6287468770163975</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.001996500002860557</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.0111278999975184</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.02382599999691593</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>louvain_Baseline</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>louvain_Baseline_road-chesapeake</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>road-chesapeake</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>louvain</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>39</v>
-      </c>
-      <c r="F14" t="n">
-        <v>170</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.2294197031039136</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.2366089965397935</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.2366089965397924</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.0003378999972483143</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.003283500001998618</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.009585100000549573</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>louvain_Baseline</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>louvain_Baseline_sociopatterns-hypertext</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>sociopatterns-hypertext</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>louvain</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>113</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2196</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.3470290771175727</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>9</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.5152676720147695</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.5152676720147689</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.003197100006218534</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.02482579999923473</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.03766239999822574</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>louvain_Baseline</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>louvain_Baseline_SW-100-6-0d1-trial2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>SW-100-6-0d1-trial2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>louvain</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100</v>
-      </c>
-      <c r="F16" t="n">
-        <v>300</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.06060606060606061</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>7</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.6448833333333298</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.6448833333333333</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.001176999998278916</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.008294500003103167</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.01750030000403058</v>
+        <v>0.02913369999441784</v>
       </c>
     </row>
   </sheetData>
